--- a/business_surveys/034_ethical_consumerism_awareness_survey--business_surveys.xlsx
+++ b/business_surveys/034_ethical_consumerism_awareness_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'always_consider_the_environmental_impact_of_my_purchasing_decisions'}</t>
+          <t>always_consider_the_environmental_impact_of_my_purchasing_decisions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Always consider the environmental impact of my purchasing decisions'}</t>
+          <t>Always consider the environmental impact of my purchasing decisions</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'often_consider_the_environmental_impact_of_my_purchasing_decisions'}</t>
+          <t>often_consider_the_environmental_impact_of_my_purchasing_decisions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Often consider the environmental impact of my purchasing decisions'}</t>
+          <t>Often consider the environmental impact of my purchasing decisions</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_consider_the_environmental_impact_of_my_purchasing_decisions'}</t>
+          <t>sometimes_consider_the_environmental_impact_of_my_purchasing_decisions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes consider the environmental impact of my purchasing decisions'}</t>
+          <t>Sometimes consider the environmental impact of my purchasing decisions</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_consider_the_environmental_impact_of_my_purchasing_decisions'}</t>
+          <t>rarely_consider_the_environmental_impact_of_my_purchasing_decisions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely consider the environmental impact of my purchasing decisions'}</t>
+          <t>Rarely consider the environmental impact of my purchasing decisions</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'never_consider_the_environmental_impact_of_my_purchasing_decisions'}</t>
+          <t>never_consider_the_environmental_impact_of_my_purchasing_decisions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Never consider the environmental impact of my purchasing decisions'}</t>
+          <t>Never consider the environmental impact of my purchasing decisions</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'buy_only_from_brands_i_know_are_sustainable'}</t>
+          <t>buy_only_from_brands_i_know_are_sustainable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Buy only from brands I know are sustainable'}</t>
+          <t>Buy only from brands I know are sustainable</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'buy_mostly_from_brands_i_know_are_sustainable'}</t>
+          <t>buy_mostly_from_brands_i_know_are_sustainable</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Buy mostly from brands I know are sustainable'}</t>
+          <t>Buy mostly from brands I know are sustainable</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'buy_some_from_brands_i_know_are_sustainable'}</t>
+          <t>buy_some_from_brands_i_know_are_sustainable</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Buy some from brands I know are sustainable'}</t>
+          <t>Buy some from brands I know are sustainable</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'buy_only_from_non-sustainable_brands'}</t>
+          <t>buy_only_from_non-sustainable_brands</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Buy only from non-sustainable brands'}</t>
+          <t>Buy only from non-sustainable brands</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'buy_mostly_from_non-sustainable_brands'}</t>
+          <t>buy_mostly_from_non-sustainable_brands</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Buy mostly from non-sustainable brands'}</t>
+          <t>Buy mostly from non-sustainable brands</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'buy_some_from_non-sustainable_brands'}</t>
+          <t>buy_some_from_non-sustainable_brands</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Buy some from non-sustainable brands'}</t>
+          <t>Buy some from non-sustainable brands</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_a_very_good_understanding_of_where_my_money_goes'}</t>
+          <t>i_have_a_very_good_understanding_of_where_my_money_goes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'I have a very good understanding of where my money goes'}</t>
+          <t>I have a very good understanding of where my money goes</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_a_good_understanding_of_where_my_money_goes'}</t>
+          <t>i_have_a_good_understanding_of_where_my_money_goes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'I have a good understanding of where my money goes'}</t>
+          <t>I have a good understanding of where my money goes</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_some_understanding_of_where_my_money_goes'}</t>
+          <t>i_have_some_understanding_of_where_my_money_goes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'I have some understanding of where my money goes'}</t>
+          <t>I have some understanding of where my money goes</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_little_understanding_of_where_my_money_goes'}</t>
+          <t>i_have_little_understanding_of_where_my_money_goes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'I have little understanding of where my money goes'}</t>
+          <t>I have little understanding of where my money goes</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_no_idea_where_my_money_goes'}</t>
+          <t>i_have_no_idea_where_my_money_goes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'I have no idea where my money goes'}</t>
+          <t>I have no idea where my money goes</t>
         </is>
       </c>
     </row>
